--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -14,7 +14,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>Test67</t>
+    <t>Test910101</t>
   </si>
 </sst>
 </file>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -12,9 +12,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>Test910101</t>
+    <t>CSI</t>
+  </si>
+  <si>
+    <t>TWH</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Temp</t>
   </si>
 </sst>
 </file>
@@ -59,13 +68,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
+      <c r="B1" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -68,7 +68,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -96,6 +96,136 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>16.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="0">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="0">
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n" s="0">
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n" s="0">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n" s="0">
+        <v>24.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n" s="0">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n" s="0">
+        <v>26.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -6,13 +6,14 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" r:id="rId3" sheetId="1"/>
+    <sheet name="Timetable" r:id="rId3" sheetId="1"/>
+    <sheet name="Subjects" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
   <si>
     <t>CSI</t>
   </si>
@@ -24,6 +25,108 @@
   </si>
   <si>
     <t>Temp</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Required Room Types</t>
+  </si>
+  <si>
+    <t>englisch</t>
+  </si>
+  <si>
+    <t>0, 0, 255</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>informationssysteme</t>
+  </si>
+  <si>
+    <t>112, 128, 144</t>
+  </si>
+  <si>
+    <t>insy</t>
+  </si>
+  <si>
+    <t>angewandte mathematik</t>
+  </si>
+  <si>
+    <t>20, 112, 250</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>recht</t>
+  </si>
+  <si>
+    <t>32, 178, 170</t>
+  </si>
+  <si>
+    <t>medientechnik film und audio</t>
+  </si>
+  <si>
+    <t>255, 192, 203</t>
+  </si>
+  <si>
+    <t>medtfi</t>
+  </si>
+  <si>
+    <t>geographie</t>
+  </si>
+  <si>
+    <t>20, 154, 88</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>medientechnik virtuelle welten und spieleentwicklung</t>
+  </si>
+  <si>
+    <t>medt3d</t>
+  </si>
+  <si>
+    <t>software entwicklung</t>
+  </si>
+  <si>
+    <t>sew</t>
+  </si>
+  <si>
+    <t>naturwissenschaften chemie</t>
+  </si>
+  <si>
+    <t>222, 209, 214</t>
+  </si>
+  <si>
+    <t>nwc</t>
+  </si>
+  <si>
+    <t>CHEM</t>
+  </si>
+  <si>
+    <t>PHY</t>
+  </si>
+  <si>
+    <t>geschichte</t>
+  </si>
+  <si>
+    <t>104, 0, 214</t>
+  </si>
+  <si>
+    <t>ges</t>
   </si>
 </sst>
 </file>
@@ -68,7 +171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -201,29 +304,331 @@
         <v>21.0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n" s="0">
-        <v>22.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n" s="0">
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n" s="0">
-        <v>24.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n" s="0">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n" s="0">
-        <v>26.0</v>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -7,15 +7,19 @@
   </bookViews>
   <sheets>
     <sheet name="Timetable" r:id="rId3" sheetId="1"/>
-    <sheet name="Subjects" r:id="rId4" sheetId="2"/>
+    <sheet name="ClassSubjects" r:id="rId4" sheetId="2"/>
+    <sheet name="Subjects" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="38">
-  <si>
-    <t>CSI</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
+  <si>
+    <t>CSI Id</t>
+  </si>
+  <si>
+    <t>CS Id</t>
   </si>
   <si>
     <t>TWH</t>
@@ -27,9 +31,105 @@
     <t>Temp</t>
   </si>
   <si>
+    <t>SchoolClass Id</t>
+  </si>
+  <si>
+    <t>SchoolClass Name</t>
+  </si>
+  <si>
+    <t>4chitm</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Subject Id</t>
+  </si>
+  <si>
+    <t>Subject Symbol</t>
+  </si>
+  <si>
+    <t>Teacher Id</t>
+  </si>
+  <si>
+    <t>Teacher Symbol</t>
+  </si>
+  <si>
+    <t>Weekly Hours</t>
+  </si>
+  <si>
+    <t>Requires Double Period</t>
+  </si>
+  <si>
+    <t>Is better as Double Period</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>insy</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>recht</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>medtfi</t>
+  </si>
+  <si>
+    <t>JW</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>JF</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>medt3d</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>sew</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>nwc</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>ges</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -42,13 +142,85 @@
     <t>Required Room Types</t>
   </si>
   <si>
+    <t>angewandte mathematik</t>
+  </si>
+  <si>
+    <t>20, 112, 250</t>
+  </si>
+  <si>
+    <t>naturwissenschaften physik</t>
+  </si>
+  <si>
+    <t>0, 207, 214</t>
+  </si>
+  <si>
+    <t>nwp</t>
+  </si>
+  <si>
+    <t>PHY</t>
+  </si>
+  <si>
+    <t>geschichte</t>
+  </si>
+  <si>
+    <t>104, 0, 214</t>
+  </si>
+  <si>
+    <t>biologie</t>
+  </si>
+  <si>
+    <t>34, 139, 34</t>
+  </si>
+  <si>
+    <t>bio</t>
+  </si>
+  <si>
+    <t>naturwissenschaften chemie</t>
+  </si>
+  <si>
+    <t>222, 209, 214</t>
+  </si>
+  <si>
+    <t>CHEM</t>
+  </si>
+  <si>
+    <t>32, 178, 170</t>
+  </si>
+  <si>
+    <t>wirtschaft</t>
+  </si>
+  <si>
+    <t>219, 203, 46</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
     <t>englisch</t>
   </si>
   <si>
     <t>0, 0, 255</t>
   </si>
   <si>
-    <t>eng</t>
+    <t>geographie</t>
+  </si>
+  <si>
+    <t>20, 154, 88</t>
+  </si>
+  <si>
+    <t>software entwicklung</t>
+  </si>
+  <si>
+    <t>255, 192, 203</t>
+  </si>
+  <si>
+    <t>deutsch</t>
+  </si>
+  <si>
+    <t>201, 0, 0</t>
+  </si>
+  <si>
+    <t>de</t>
   </si>
   <si>
     <t>informationssysteme</t>
@@ -57,76 +229,46 @@
     <t>112, 128, 144</t>
   </si>
   <si>
-    <t>insy</t>
-  </si>
-  <si>
-    <t>angewandte mathematik</t>
-  </si>
-  <si>
-    <t>20, 112, 250</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t>recht</t>
-  </si>
-  <si>
-    <t>32, 178, 170</t>
+    <t>informationstechnische projekte</t>
+  </si>
+  <si>
+    <t>255, 165, 0</t>
+  </si>
+  <si>
+    <t>itp</t>
+  </si>
+  <si>
+    <t>religion</t>
+  </si>
+  <si>
+    <t>174, 115, 127</t>
+  </si>
+  <si>
+    <t>rel</t>
+  </si>
+  <si>
+    <t>medientechnik print und design</t>
+  </si>
+  <si>
+    <t>medtpd</t>
+  </si>
+  <si>
+    <t>medientechnik mobile computing</t>
+  </si>
+  <si>
+    <t>medtmc</t>
   </si>
   <si>
     <t>medientechnik film und audio</t>
   </si>
   <si>
-    <t>255, 192, 203</t>
-  </si>
-  <si>
-    <t>medtfi</t>
-  </si>
-  <si>
-    <t>geographie</t>
-  </si>
-  <si>
-    <t>20, 154, 88</t>
-  </si>
-  <si>
-    <t>geo</t>
+    <t>medientechnik social media</t>
+  </si>
+  <si>
+    <t>medtsm</t>
   </si>
   <si>
     <t>medientechnik virtuelle welten und spieleentwicklung</t>
-  </si>
-  <si>
-    <t>medt3d</t>
-  </si>
-  <si>
-    <t>software entwicklung</t>
-  </si>
-  <si>
-    <t>sew</t>
-  </si>
-  <si>
-    <t>naturwissenschaften chemie</t>
-  </si>
-  <si>
-    <t>222, 209, 214</t>
-  </si>
-  <si>
-    <t>nwc</t>
-  </si>
-  <si>
-    <t>CHEM</t>
-  </si>
-  <si>
-    <t>PHY</t>
-  </si>
-  <si>
-    <t>geschichte</t>
-  </si>
-  <si>
-    <t>104, 0, 214</t>
-  </si>
-  <si>
-    <t>ges</t>
   </si>
 </sst>
 </file>
@@ -171,7 +313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -187,121 +329,183 @@
       <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
+      <c r="E1" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
-      <c r="B2" t="n" s="0">
-        <v>0.0</v>
-      </c>
       <c r="C2" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>0.0</v>
+      </c>
+      <c r="E2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
         <v>1.0</v>
       </c>
+      <c r="B3" t="n" s="0">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n" s="0">
         <v>2.0</v>
       </c>
+      <c r="B4" t="n" s="0">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n" s="0">
         <v>3.0</v>
       </c>
+      <c r="B5" t="n" s="0">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n" s="0">
         <v>4.0</v>
       </c>
+      <c r="B6" t="n" s="0">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n" s="0">
         <v>5.0</v>
       </c>
+      <c r="B7" t="n" s="0">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n" s="0">
         <v>6.0</v>
       </c>
+      <c r="B8" t="n" s="0">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n" s="0">
         <v>7.0</v>
       </c>
+      <c r="B9" t="n" s="0">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n" s="0">
         <v>8.0</v>
       </c>
+      <c r="B10" t="n" s="0">
+        <v>7.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n" s="0">
         <v>9.0</v>
       </c>
+      <c r="B11" t="n" s="0">
+        <v>8.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n" s="0">
         <v>10.0</v>
       </c>
+      <c r="B12" t="n" s="0">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n" s="0">
         <v>11.0</v>
       </c>
+      <c r="B13" t="n" s="0">
+        <v>9.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n" s="0">
         <v>12.0</v>
       </c>
+      <c r="B14" t="n" s="0">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n" s="0">
         <v>13.0</v>
       </c>
+      <c r="B15" t="n" s="0">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n" s="0">
         <v>14.0</v>
       </c>
+      <c r="B16" t="n" s="0">
+        <v>11.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n" s="0">
         <v>15.0</v>
       </c>
+      <c r="B17" t="n" s="0">
+        <v>11.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n" s="0">
         <v>16.0</v>
       </c>
+      <c r="B18" t="n" s="0">
+        <v>12.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n" s="0">
         <v>17.0</v>
       </c>
+      <c r="B19" t="n" s="0">
+        <v>13.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n" s="0">
         <v>18.0</v>
       </c>
+      <c r="B20" t="n" s="0">
+        <v>14.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n" s="0">
         <v>19.0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n" s="0">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n" s="0">
-        <v>21.0</v>
+      <c r="B21" t="n" s="0">
+        <v>14.0</v>
       </c>
     </row>
   </sheetData>
@@ -311,324 +515,699 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>15</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
         <v>8.0</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>9</v>
-      </c>
       <c r="C2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>11</v>
+        <v>16</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G2" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
         <v>12.0</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>12</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>12</v>
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>1.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>17</v>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>17</v>
+      <c r="G6" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n" s="0">
         <v>6.0</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>18</v>
+      <c r="B7" t="n" s="0">
+        <v>9.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>18</v>
+        <v>26</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>20</v>
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>9.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>23</v>
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>8.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n" s="0">
         <v>9.0</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>23</v>
+      <c r="B10" t="n" s="0">
+        <v>8.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s" s="0">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D11" t="n" s="0">
         <v>9.0</v>
       </c>
-      <c r="B11" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>25</v>
+      <c r="E11" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="B12" t="s" s="0">
-        <v>9</v>
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="n" s="0">
+        <v>19.0</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s" s="0">
-        <v>11</v>
+        <v>31</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="B13" t="s" s="0">
-        <v>9</v>
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="n" s="0">
+        <v>10.0</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s" s="0">
-        <v>11</v>
+        <v>33</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="B14" t="s" s="0">
-        <v>18</v>
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="n" s="0">
+        <v>5.0</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s" s="0">
-        <v>18</v>
+        <v>35</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G14" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
         <v>6.0</v>
       </c>
+      <c r="B7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
       <c r="B15" t="s" s="0">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>18</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n" s="0">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>27</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n" s="0">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>27</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n" s="0">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n" s="0">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>29</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n" s="0">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="B21" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s" s="0">
         <v>31</v>
-      </c>
-      <c r="D21" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="E21" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="F21" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="B22" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s" s="0">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Timetable" r:id="rId3" sheetId="1"/>
     <sheet name="ClassSubjects" r:id="rId4" sheetId="2"/>
     <sheet name="Subjects" r:id="rId5" sheetId="3"/>
+    <sheet name="Rooms" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="110">
   <si>
     <t>CSI Id</t>
   </si>
@@ -22,7 +23,7 @@
     <t>CS Id</t>
   </si>
   <si>
-    <t>TWH</t>
+    <t>Total weekly hours</t>
   </si>
   <si>
     <t>Cost</t>
@@ -269,6 +270,81 @@
   </si>
   <si>
     <t>medientechnik virtuelle welten und spieleentwicklung</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Room Type</t>
+  </si>
+  <si>
+    <t>potts</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>WORKSHOP</t>
+  </si>
+  <si>
+    <t>vincent</t>
+  </si>
+  <si>
+    <t>vin</t>
+  </si>
+  <si>
+    <t>williams</t>
+  </si>
+  <si>
+    <t>wil</t>
+  </si>
+  <si>
+    <t>morgan</t>
+  </si>
+  <si>
+    <t>mor</t>
+  </si>
+  <si>
+    <t>CLASSROOM</t>
+  </si>
+  <si>
+    <t>hernandez</t>
+  </si>
+  <si>
+    <t>her</t>
+  </si>
+  <si>
+    <t>SPORT</t>
+  </si>
+  <si>
+    <t>EDV</t>
+  </si>
+  <si>
+    <t>cervantes</t>
+  </si>
+  <si>
+    <t>cer</t>
+  </si>
+  <si>
+    <t>mercado</t>
+  </si>
+  <si>
+    <t>mer</t>
+  </si>
+  <si>
+    <t>stanton</t>
+  </si>
+  <si>
+    <t>sta</t>
+  </si>
+  <si>
+    <t>russell</t>
+  </si>
+  <si>
+    <t>rus</t>
   </si>
 </sst>
 </file>
@@ -313,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -369,7 +445,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -377,7 +453,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -417,7 +493,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="11">
@@ -425,7 +501,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="12">
@@ -433,7 +509,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="13">
@@ -441,7 +517,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="14">
@@ -449,7 +525,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="15">
@@ -465,7 +541,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="17">
@@ -481,7 +557,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="19">
@@ -489,7 +565,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="20">
@@ -497,7 +573,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="21">
@@ -505,6 +581,22 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="n" s="0">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B22" t="n" s="0">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="B23" t="n" s="0">
         <v>14.0</v>
       </c>
     </row>
@@ -1213,4 +1305,216 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>66.0</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>480.0</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>447.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>256.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>313.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>421.0</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>323.0</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>398.0</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>488.0</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>125.0</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -10,12 +10,13 @@
     <sheet name="ClassSubjects" r:id="rId4" sheetId="2"/>
     <sheet name="Subjects" r:id="rId5" sheetId="3"/>
     <sheet name="Rooms" r:id="rId6" sheetId="4"/>
+    <sheet name="Teachers" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="159">
   <si>
     <t>CSI Id</t>
   </si>
@@ -345,6 +346,153 @@
   </si>
   <si>
     <t>rus</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Teaching Subjects Ids</t>
+  </si>
+  <si>
+    <t>Teaching Subjects Symbols</t>
+  </si>
+  <si>
+    <t>Jill Patterson</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11, </t>
+  </si>
+  <si>
+    <t>Christopher Cochran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16, 19, 8, </t>
+  </si>
+  <si>
+    <t>Shane Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13, </t>
+  </si>
+  <si>
+    <t>Austin Burton</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19, 14, 9, </t>
+  </si>
+  <si>
+    <t>Sean Burnett</t>
+  </si>
+  <si>
+    <t>Abigail Sullivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8, 2, </t>
+  </si>
+  <si>
+    <t>Teresa Baker</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 17, </t>
+  </si>
+  <si>
+    <t>James Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19, </t>
+  </si>
+  <si>
+    <t>Monique Ware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19, 15, 7, </t>
+  </si>
+  <si>
+    <t>Sarah Rivera</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 13, 14, </t>
+  </si>
+  <si>
+    <t>Samantha Larson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10, </t>
+  </si>
+  <si>
+    <t>Scott Duffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15, </t>
+  </si>
+  <si>
+    <t>Andrew Jackson</t>
+  </si>
+  <si>
+    <t>AJ</t>
+  </si>
+  <si>
+    <t>Michael Mckinney</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19, 4, 5, </t>
+  </si>
+  <si>
+    <t>Brian Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4, </t>
+  </si>
+  <si>
+    <t>Steven Martinez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5, 1, </t>
+  </si>
+  <si>
+    <t>Jordan Fletcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14, 15, 9, </t>
+  </si>
+  <si>
+    <t>Riley Gutierrez</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4, 8, 3, </t>
+  </si>
+  <si>
+    <t>Nathan King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5, 17, </t>
+  </si>
+  <si>
+    <t>Jake Kelley</t>
+  </si>
+  <si>
+    <t>JK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13, 3, 17, </t>
   </si>
 </sst>
 </file>
@@ -389,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -445,7 +593,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +601,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
@@ -461,7 +609,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="7">
@@ -469,7 +617,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="8">
@@ -477,7 +625,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="9">
@@ -485,7 +633,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +641,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="11">
@@ -501,7 +649,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="12">
@@ -517,7 +665,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="14">
@@ -525,7 +673,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="15">
@@ -541,7 +689,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="17">
@@ -549,7 +697,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="18">
@@ -557,7 +705,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="19">
@@ -565,7 +713,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="20">
@@ -573,7 +721,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="21">
@@ -581,7 +729,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="22">
@@ -589,14 +737,6 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="B23" t="n" s="0">
         <v>14.0</v>
       </c>
     </row>
@@ -1517,4 +1657,311 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="177">
   <si>
     <t>CSI Id</t>
   </si>
@@ -366,18 +366,27 @@
     <t xml:space="preserve">11, </t>
   </si>
   <si>
+    <t xml:space="preserve">de, </t>
+  </si>
+  <si>
     <t>Christopher Cochran</t>
   </si>
   <si>
     <t xml:space="preserve">16, 19, 8, </t>
   </si>
   <si>
+    <t xml:space="preserve">medtmc, medt3d, eng, </t>
+  </si>
+  <si>
     <t>Shane Allen</t>
   </si>
   <si>
     <t xml:space="preserve">13, </t>
   </si>
   <si>
+    <t xml:space="preserve">itp, </t>
+  </si>
+  <si>
     <t>Austin Burton</t>
   </si>
   <si>
@@ -387,6 +396,9 @@
     <t xml:space="preserve">19, 14, 9, </t>
   </si>
   <si>
+    <t xml:space="preserve">medt3d, rel, geo, </t>
+  </si>
+  <si>
     <t>Sean Burnett</t>
   </si>
   <si>
@@ -396,6 +408,9 @@
     <t xml:space="preserve">8, 2, </t>
   </si>
   <si>
+    <t xml:space="preserve">eng, nwp, </t>
+  </si>
+  <si>
     <t>Teresa Baker</t>
   </si>
   <si>
@@ -405,18 +420,27 @@
     <t xml:space="preserve">2, 17, </t>
   </si>
   <si>
+    <t xml:space="preserve">nwp, medtfi, </t>
+  </si>
+  <si>
     <t>James Wood</t>
   </si>
   <si>
     <t xml:space="preserve">19, </t>
   </si>
   <si>
+    <t xml:space="preserve">medt3d, </t>
+  </si>
+  <si>
     <t>Monique Ware</t>
   </si>
   <si>
     <t xml:space="preserve">19, 15, 7, </t>
   </si>
   <si>
+    <t xml:space="preserve">medt3d, medtpd, wt, </t>
+  </si>
+  <si>
     <t>Sarah Rivera</t>
   </si>
   <si>
@@ -426,18 +450,27 @@
     <t xml:space="preserve">2, 13, 14, </t>
   </si>
   <si>
+    <t xml:space="preserve">nwp, itp, rel, </t>
+  </si>
+  <si>
     <t>Samantha Larson</t>
   </si>
   <si>
     <t xml:space="preserve">10, </t>
   </si>
   <si>
+    <t xml:space="preserve">sew, </t>
+  </si>
+  <si>
     <t>Scott Duffy</t>
   </si>
   <si>
     <t xml:space="preserve">15, </t>
   </si>
   <si>
+    <t xml:space="preserve">medtpd, </t>
+  </si>
+  <si>
     <t>Andrew Jackson</t>
   </si>
   <si>
@@ -453,24 +486,36 @@
     <t xml:space="preserve">19, 4, 5, </t>
   </si>
   <si>
+    <t xml:space="preserve">medt3d, bio, nwc, </t>
+  </si>
+  <si>
     <t>Brian Wood</t>
   </si>
   <si>
     <t xml:space="preserve">4, </t>
   </si>
   <si>
+    <t xml:space="preserve">bio, </t>
+  </si>
+  <si>
     <t>Steven Martinez</t>
   </si>
   <si>
     <t xml:space="preserve">5, 1, </t>
   </si>
   <si>
+    <t xml:space="preserve">nwc, am, </t>
+  </si>
+  <si>
     <t>Jordan Fletcher</t>
   </si>
   <si>
     <t xml:space="preserve">14, 15, 9, </t>
   </si>
   <si>
+    <t xml:space="preserve">rel, medtpd, geo, </t>
+  </si>
+  <si>
     <t>Riley Gutierrez</t>
   </si>
   <si>
@@ -480,12 +525,18 @@
     <t xml:space="preserve">4, 8, 3, </t>
   </si>
   <si>
+    <t xml:space="preserve">bio, eng, ges, </t>
+  </si>
+  <si>
     <t>Nathan King</t>
   </si>
   <si>
     <t xml:space="preserve">5, 17, </t>
   </si>
   <si>
+    <t xml:space="preserve">nwc, medtfi, </t>
+  </si>
+  <si>
     <t>Jake Kelley</t>
   </si>
   <si>
@@ -493,6 +544,9 @@
   </si>
   <si>
     <t xml:space="preserve">13, 3, 17, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">itp, ges, medtfi, </t>
   </si>
 </sst>
 </file>
@@ -593,7 +647,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +655,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +663,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="7">
@@ -617,7 +671,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +679,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="9">
@@ -633,7 +687,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +695,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="11">
@@ -649,7 +703,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="12">
@@ -657,7 +711,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="13">
@@ -665,7 +719,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="14">
@@ -673,7 +727,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="15">
@@ -713,7 +767,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="20">
@@ -721,7 +775,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="21">
@@ -1694,19 +1748,25 @@
       <c r="D2" t="s" s="0">
         <v>115</v>
       </c>
+      <c r="E2" t="s" s="0">
+        <v>116</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>28</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -1714,13 +1774,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>19</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -1728,13 +1791,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>122</v>
+        <v>125</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -1742,13 +1808,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
         <v>115</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -1756,13 +1825,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>125</v>
+        <v>129</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>130</v>
       </c>
     </row>
     <row r="8">
@@ -1770,13 +1842,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>128</v>
+        <v>133</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>134</v>
       </c>
     </row>
     <row r="9">
@@ -1784,13 +1859,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>25</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>130</v>
+        <v>136</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -1798,13 +1876,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>30</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>132</v>
+        <v>139</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -1812,13 +1893,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>135</v>
+        <v>143</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>144</v>
       </c>
     </row>
     <row r="12">
@@ -1826,13 +1910,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>17</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>137</v>
+        <v>146</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -1840,13 +1927,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>36</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>139</v>
+        <v>149</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>150</v>
       </c>
     </row>
     <row r="14">
@@ -1854,13 +1944,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s" s="0">
         <v>115</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1868,13 +1961,16 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>144</v>
+        <v>155</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>156</v>
       </c>
     </row>
     <row r="16">
@@ -1882,13 +1978,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>146</v>
+        <v>158</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>159</v>
       </c>
     </row>
     <row r="17">
@@ -1896,13 +1995,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>27</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>148</v>
+        <v>161</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>162</v>
       </c>
     </row>
     <row r="18">
@@ -1910,13 +2012,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>29</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>150</v>
+        <v>164</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>165</v>
       </c>
     </row>
     <row r="19">
@@ -1924,13 +2029,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>153</v>
+        <v>168</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>169</v>
       </c>
     </row>
     <row r="20">
@@ -1938,13 +2046,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>155</v>
+        <v>171</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>172</v>
       </c>
     </row>
     <row r="21">
@@ -1952,13 +2063,16 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>158</v>
+        <v>175</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="159">
   <si>
     <t>CSI Id</t>
   </si>
@@ -135,9 +135,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Color</t>
-  </si>
-  <si>
     <t>Symbol</t>
   </si>
   <si>
@@ -147,15 +144,12 @@
     <t>angewandte mathematik</t>
   </si>
   <si>
-    <t>20, 112, 250</t>
+    <t/>
   </si>
   <si>
     <t>naturwissenschaften physik</t>
   </si>
   <si>
-    <t>0, 207, 214</t>
-  </si>
-  <si>
     <t>nwp</t>
   </si>
   <si>
@@ -165,87 +159,51 @@
     <t>geschichte</t>
   </si>
   <si>
-    <t>104, 0, 214</t>
-  </si>
-  <si>
     <t>biologie</t>
   </si>
   <si>
-    <t>34, 139, 34</t>
-  </si>
-  <si>
     <t>bio</t>
   </si>
   <si>
     <t>naturwissenschaften chemie</t>
   </si>
   <si>
-    <t>222, 209, 214</t>
-  </si>
-  <si>
-    <t>CHEM</t>
-  </si>
-  <si>
-    <t>32, 178, 170</t>
+    <t>CHEM, PHY</t>
   </si>
   <si>
     <t>wirtschaft</t>
   </si>
   <si>
-    <t>219, 203, 46</t>
-  </si>
-  <si>
     <t>wt</t>
   </si>
   <si>
     <t>englisch</t>
   </si>
   <si>
-    <t>0, 0, 255</t>
-  </si>
-  <si>
     <t>geographie</t>
   </si>
   <si>
-    <t>20, 154, 88</t>
-  </si>
-  <si>
     <t>software entwicklung</t>
   </si>
   <si>
-    <t>255, 192, 203</t>
-  </si>
-  <si>
     <t>deutsch</t>
   </si>
   <si>
-    <t>201, 0, 0</t>
-  </si>
-  <si>
     <t>de</t>
   </si>
   <si>
     <t>informationssysteme</t>
   </si>
   <si>
-    <t>112, 128, 144</t>
-  </si>
-  <si>
     <t>informationstechnische projekte</t>
   </si>
   <si>
-    <t>255, 165, 0</t>
-  </si>
-  <si>
     <t>itp</t>
   </si>
   <si>
     <t>religion</t>
   </si>
   <si>
-    <t>174, 115, 127</t>
-  </si>
-  <si>
     <t>rel</t>
   </si>
   <si>
@@ -309,7 +267,7 @@
     <t>mor</t>
   </si>
   <si>
-    <t>CLASSROOM</t>
+    <t>WORKSHOP, CLASSROOM</t>
   </si>
   <si>
     <t>hernandez</t>
@@ -318,24 +276,30 @@
     <t>her</t>
   </si>
   <si>
+    <t>SPORT, EDV</t>
+  </si>
+  <si>
+    <t>CLASSROOM, WORKSHOP</t>
+  </si>
+  <si>
+    <t>cervantes</t>
+  </si>
+  <si>
+    <t>cer</t>
+  </si>
+  <si>
     <t>SPORT</t>
   </si>
   <si>
-    <t>EDV</t>
-  </si>
-  <si>
-    <t>cervantes</t>
-  </si>
-  <si>
-    <t>cer</t>
-  </si>
-  <si>
     <t>mercado</t>
   </si>
   <si>
     <t>mer</t>
   </si>
   <si>
+    <t>SPORT, WORKSHOP</t>
+  </si>
+  <si>
     <t>stanton</t>
   </si>
   <si>
@@ -363,28 +327,22 @@
     <t>JP</t>
   </si>
   <si>
-    <t xml:space="preserve">11, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">de, </t>
+    <t>11</t>
   </si>
   <si>
     <t>Christopher Cochran</t>
   </si>
   <si>
-    <t xml:space="preserve">16, 19, 8, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medtmc, medt3d, eng, </t>
+    <t>16, 19, 8</t>
+  </si>
+  <si>
+    <t>medtmc, medt3d, eng</t>
   </si>
   <si>
     <t>Shane Allen</t>
   </si>
   <si>
-    <t xml:space="preserve">13, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">itp, </t>
+    <t>13</t>
   </si>
   <si>
     <t>Austin Burton</t>
@@ -393,10 +351,10 @@
     <t>AB</t>
   </si>
   <si>
-    <t xml:space="preserve">19, 14, 9, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medt3d, rel, geo, </t>
+    <t>19, 14, 9</t>
+  </si>
+  <si>
+    <t>medt3d, rel, geo</t>
   </si>
   <si>
     <t>Sean Burnett</t>
@@ -405,10 +363,10 @@
     <t>Abigail Sullivan</t>
   </si>
   <si>
-    <t xml:space="preserve">8, 2, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">eng, nwp, </t>
+    <t>8, 2</t>
+  </si>
+  <si>
+    <t>eng, nwp</t>
   </si>
   <si>
     <t>Teresa Baker</t>
@@ -417,28 +375,25 @@
     <t>TB</t>
   </si>
   <si>
-    <t xml:space="preserve">2, 17, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nwp, medtfi, </t>
+    <t>2, 17</t>
+  </si>
+  <si>
+    <t>nwp, medtfi</t>
   </si>
   <si>
     <t>James Wood</t>
   </si>
   <si>
-    <t xml:space="preserve">19, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medt3d, </t>
+    <t>19</t>
   </si>
   <si>
     <t>Monique Ware</t>
   </si>
   <si>
-    <t xml:space="preserve">19, 15, 7, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medt3d, medtpd, wt, </t>
+    <t>19, 15, 7</t>
+  </si>
+  <si>
+    <t>medt3d, medtpd, wt</t>
   </si>
   <si>
     <t>Sarah Rivera</t>
@@ -447,28 +402,22 @@
     <t>SR</t>
   </si>
   <si>
-    <t xml:space="preserve">2, 13, 14, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nwp, itp, rel, </t>
+    <t>2, 13, 14</t>
+  </si>
+  <si>
+    <t>nwp, itp, rel</t>
   </si>
   <si>
     <t>Samantha Larson</t>
   </si>
   <si>
-    <t xml:space="preserve">10, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">sew, </t>
+    <t>10</t>
   </si>
   <si>
     <t>Scott Duffy</t>
   </si>
   <si>
-    <t xml:space="preserve">15, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medtpd, </t>
+    <t>15</t>
   </si>
   <si>
     <t>Andrew Jackson</t>
@@ -483,37 +432,34 @@
     <t>MM</t>
   </si>
   <si>
-    <t xml:space="preserve">19, 4, 5, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medt3d, bio, nwc, </t>
+    <t>19, 4, 5</t>
+  </si>
+  <si>
+    <t>medt3d, bio, nwc</t>
   </si>
   <si>
     <t>Brian Wood</t>
   </si>
   <si>
-    <t xml:space="preserve">4, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">bio, </t>
+    <t>4</t>
   </si>
   <si>
     <t>Steven Martinez</t>
   </si>
   <si>
-    <t xml:space="preserve">5, 1, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nwc, am, </t>
+    <t>5, 1</t>
+  </si>
+  <si>
+    <t>nwc, am</t>
   </si>
   <si>
     <t>Jordan Fletcher</t>
   </si>
   <si>
-    <t xml:space="preserve">14, 15, 9, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rel, medtpd, geo, </t>
+    <t>14, 15, 9</t>
+  </si>
+  <si>
+    <t>rel, medtpd, geo</t>
   </si>
   <si>
     <t>Riley Gutierrez</t>
@@ -522,19 +468,19 @@
     <t>RG</t>
   </si>
   <si>
-    <t xml:space="preserve">4, 8, 3, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">bio, eng, ges, </t>
+    <t>4, 8, 3</t>
+  </si>
+  <si>
+    <t>bio, eng, ges</t>
   </si>
   <si>
     <t>Nathan King</t>
   </si>
   <si>
-    <t xml:space="preserve">5, 17, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nwc, medtfi, </t>
+    <t>5, 17</t>
+  </si>
+  <si>
+    <t>nwc, medtfi</t>
   </si>
   <si>
     <t>Jake Kelley</t>
@@ -543,10 +489,10 @@
     <t>JK</t>
   </si>
   <si>
-    <t xml:space="preserve">13, 3, 17, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">itp, ges, medtfi, </t>
+    <t>13, 3, 17</t>
+  </si>
+  <si>
+    <t>itp, ges, medtfi</t>
   </si>
 </sst>
 </file>
@@ -647,7 +593,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
@@ -655,7 +601,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
@@ -671,7 +617,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8">
@@ -679,7 +625,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +633,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +641,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="11">
@@ -703,7 +649,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="12">
@@ -711,7 +657,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="13">
@@ -719,7 +665,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="14">
@@ -751,7 +697,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="18">
@@ -1201,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1217,22 +1163,19 @@
       <c r="D1" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="E1" t="s" s="0">
-        <v>41</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s" s="0">
         <v>42</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1240,16 +1183,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="D3" t="s" s="0">
         <v>45</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -1257,13 +1197,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -1271,13 +1211,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -1285,19 +1225,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1308,10 +1242,10 @@
         <v>22</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -1319,13 +1253,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1333,13 +1267,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -1347,13 +1281,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -1361,13 +1295,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -1375,13 +1309,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -1389,13 +1323,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -1403,13 +1337,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -1417,13 +1351,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>76</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -1431,13 +1365,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>78</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -1445,13 +1379,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -1459,13 +1393,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -1473,13 +1407,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -1487,13 +1421,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1503,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1511,16 +1445,16 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>38</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -1531,13 +1465,13 @@
         <v>66.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -1548,13 +1482,13 @@
         <v>480.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -1565,16 +1499,13 @@
         <v>447.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1585,16 +1516,13 @@
         <v>256.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -1605,16 +1533,13 @@
         <v>313.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -1625,16 +1550,13 @@
         <v>421.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -1645,13 +1567,13 @@
         <v>323.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -1662,16 +1584,13 @@
         <v>398.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -1682,13 +1601,13 @@
         <v>488.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -1699,13 +1618,13 @@
         <v>125.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1720,19 +1639,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>38</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -1740,16 +1659,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -1757,16 +1676,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>28</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -1774,16 +1693,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>19</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>122</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1791,16 +1710,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -1808,16 +1727,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1825,16 +1744,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>21</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>130</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -1842,16 +1761,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>134</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -1859,16 +1778,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>25</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>137</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -1876,16 +1795,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s" s="0">
         <v>30</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -1893,16 +1812,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -1910,16 +1829,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>17</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>147</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -1927,16 +1846,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>36</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>150</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -1944,16 +1863,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -1961,16 +1880,16 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>156</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16">
@@ -1978,16 +1897,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>159</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1995,16 +1914,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>27</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18">
@@ -2012,16 +1931,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s" s="0">
         <v>29</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s" s="0">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19">
@@ -2029,16 +1948,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s" s="0">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
@@ -2046,16 +1965,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s" s="0">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s" s="0">
-        <v>172</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -2063,16 +1982,16 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s" s="0">
-        <v>176</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="153">
   <si>
     <t>CSI Id</t>
   </si>
@@ -48,13 +48,7 @@
     <t>Subject Id</t>
   </si>
   <si>
-    <t>Subject Symbol</t>
-  </si>
-  <si>
-    <t>Teacher Id</t>
-  </si>
-  <si>
-    <t>Teacher Symbol</t>
+    <t>Teacher Ids</t>
   </si>
   <si>
     <t>Weekly Hours</t>
@@ -66,423 +60,414 @@
     <t>Is better as Double Period</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Required Room Types</t>
+  </si>
+  <si>
+    <t>angewandte mathematik</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>naturwissenschaften physik</t>
+  </si>
+  <si>
+    <t>nwp</t>
+  </si>
+  <si>
+    <t>PHY</t>
+  </si>
+  <si>
+    <t>geschichte</t>
+  </si>
+  <si>
+    <t>ges</t>
+  </si>
+  <si>
+    <t>biologie</t>
+  </si>
+  <si>
+    <t>bio</t>
+  </si>
+  <si>
+    <t>naturwissenschaften chemie</t>
+  </si>
+  <si>
+    <t>nwc</t>
+  </si>
+  <si>
+    <t>CHEM, PHY</t>
+  </si>
+  <si>
+    <t>recht</t>
+  </si>
+  <si>
+    <t>wirtschaft</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>englisch</t>
+  </si>
+  <si>
     <t>eng</t>
   </si>
   <si>
+    <t>geographie</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>software entwicklung</t>
+  </si>
+  <si>
+    <t>sew</t>
+  </si>
+  <si>
+    <t>deutsch</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>informationssysteme</t>
+  </si>
+  <si>
+    <t>insy</t>
+  </si>
+  <si>
+    <t>informationstechnische projekte</t>
+  </si>
+  <si>
+    <t>itp</t>
+  </si>
+  <si>
+    <t>religion</t>
+  </si>
+  <si>
+    <t>rel</t>
+  </si>
+  <si>
+    <t>medientechnik print und design</t>
+  </si>
+  <si>
+    <t>medtpd</t>
+  </si>
+  <si>
+    <t>medientechnik mobile computing</t>
+  </si>
+  <si>
+    <t>medtmc</t>
+  </si>
+  <si>
+    <t>medientechnik film und audio</t>
+  </si>
+  <si>
+    <t>medtfi</t>
+  </si>
+  <si>
+    <t>medientechnik social media</t>
+  </si>
+  <si>
+    <t>medtsm</t>
+  </si>
+  <si>
+    <t>medientechnik virtuelle welten und spieleentwicklung</t>
+  </si>
+  <si>
+    <t>medt3d</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Room Type</t>
+  </si>
+  <si>
+    <t>potts</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>WORKSHOP</t>
+  </si>
+  <si>
+    <t>vincent</t>
+  </si>
+  <si>
+    <t>vin</t>
+  </si>
+  <si>
+    <t>williams</t>
+  </si>
+  <si>
+    <t>wil</t>
+  </si>
+  <si>
+    <t>morgan</t>
+  </si>
+  <si>
+    <t>mor</t>
+  </si>
+  <si>
+    <t>WORKSHOP, CLASSROOM</t>
+  </si>
+  <si>
+    <t>hernandez</t>
+  </si>
+  <si>
+    <t>her</t>
+  </si>
+  <si>
+    <t>SPORT, EDV</t>
+  </si>
+  <si>
+    <t>CLASSROOM, WORKSHOP</t>
+  </si>
+  <si>
+    <t>cervantes</t>
+  </si>
+  <si>
+    <t>cer</t>
+  </si>
+  <si>
+    <t>SPORT</t>
+  </si>
+  <si>
+    <t>mercado</t>
+  </si>
+  <si>
+    <t>mer</t>
+  </si>
+  <si>
+    <t>SPORT, WORKSHOP</t>
+  </si>
+  <si>
+    <t>stanton</t>
+  </si>
+  <si>
+    <t>sta</t>
+  </si>
+  <si>
+    <t>russell</t>
+  </si>
+  <si>
+    <t>rus</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Teaching Subjects Ids</t>
+  </si>
+  <si>
+    <t>Jill Patterson</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>Christopher Cochran</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>16, 19, 8</t>
+  </si>
+  <si>
+    <t>Shane Allen</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Austin Burton</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>19, 14, 9</t>
+  </si>
+  <si>
+    <t>Sean Burnett</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>Abigail Sullivan</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>8, 2</t>
+  </si>
+  <si>
+    <t>Teresa Baker</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>2, 17</t>
+  </si>
+  <si>
+    <t>James Wood</t>
+  </si>
+  <si>
+    <t>JW</t>
+  </si>
+  <si>
+    <t>Monique Ware</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>19, 15, 7</t>
+  </si>
+  <si>
+    <t>Sarah Rivera</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>2, 13, 14</t>
+  </si>
+  <si>
+    <t>Samantha Larson</t>
+  </si>
+  <si>
     <t>SL</t>
   </si>
   <si>
-    <t>insy</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>recht</t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
-    <t>medtfi</t>
-  </si>
-  <si>
-    <t>JW</t>
-  </si>
-  <si>
-    <t>geo</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scott Duffy</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Andrew Jackson</t>
+  </si>
+  <si>
+    <t>AJ</t>
+  </si>
+  <si>
+    <t>Michael Mckinney</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>19, 4, 5</t>
+  </si>
+  <si>
+    <t>Brian Wood</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Steven Martinez</t>
   </si>
   <si>
     <t>SM</t>
   </si>
   <si>
-    <t>CC</t>
+    <t>5, 1</t>
+  </si>
+  <si>
+    <t>Jordan Fletcher</t>
   </si>
   <si>
     <t>JF</t>
   </si>
   <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>medt3d</t>
+    <t>14, 15, 9</t>
+  </si>
+  <si>
+    <t>Riley Gutierrez</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>4, 8, 3</t>
+  </si>
+  <si>
+    <t>Nathan King</t>
   </si>
   <si>
     <t>NK</t>
   </si>
   <si>
-    <t>sew</t>
-  </si>
-  <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>nwc</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>ges</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Symbol</t>
-  </si>
-  <si>
-    <t>Required Room Types</t>
-  </si>
-  <si>
-    <t>angewandte mathematik</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>naturwissenschaften physik</t>
-  </si>
-  <si>
-    <t>nwp</t>
-  </si>
-  <si>
-    <t>PHY</t>
-  </si>
-  <si>
-    <t>geschichte</t>
-  </si>
-  <si>
-    <t>biologie</t>
-  </si>
-  <si>
-    <t>bio</t>
-  </si>
-  <si>
-    <t>naturwissenschaften chemie</t>
-  </si>
-  <si>
-    <t>CHEM, PHY</t>
-  </si>
-  <si>
-    <t>wirtschaft</t>
-  </si>
-  <si>
-    <t>wt</t>
-  </si>
-  <si>
-    <t>englisch</t>
-  </si>
-  <si>
-    <t>geographie</t>
-  </si>
-  <si>
-    <t>software entwicklung</t>
-  </si>
-  <si>
-    <t>deutsch</t>
-  </si>
-  <si>
-    <t>de</t>
-  </si>
-  <si>
-    <t>informationssysteme</t>
-  </si>
-  <si>
-    <t>informationstechnische projekte</t>
-  </si>
-  <si>
-    <t>itp</t>
-  </si>
-  <si>
-    <t>religion</t>
-  </si>
-  <si>
-    <t>rel</t>
-  </si>
-  <si>
-    <t>medientechnik print und design</t>
-  </si>
-  <si>
-    <t>medtpd</t>
-  </si>
-  <si>
-    <t>medientechnik mobile computing</t>
-  </si>
-  <si>
-    <t>medtmc</t>
-  </si>
-  <si>
-    <t>medientechnik film und audio</t>
-  </si>
-  <si>
-    <t>medientechnik social media</t>
-  </si>
-  <si>
-    <t>medtsm</t>
-  </si>
-  <si>
-    <t>medientechnik virtuelle welten und spieleentwicklung</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Room Type</t>
-  </si>
-  <si>
-    <t>potts</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>WORKSHOP</t>
-  </si>
-  <si>
-    <t>vincent</t>
-  </si>
-  <si>
-    <t>vin</t>
-  </si>
-  <si>
-    <t>williams</t>
-  </si>
-  <si>
-    <t>wil</t>
-  </si>
-  <si>
-    <t>morgan</t>
-  </si>
-  <si>
-    <t>mor</t>
-  </si>
-  <si>
-    <t>WORKSHOP, CLASSROOM</t>
-  </si>
-  <si>
-    <t>hernandez</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>SPORT, EDV</t>
-  </si>
-  <si>
-    <t>CLASSROOM, WORKSHOP</t>
-  </si>
-  <si>
-    <t>cervantes</t>
-  </si>
-  <si>
-    <t>cer</t>
-  </si>
-  <si>
-    <t>SPORT</t>
-  </si>
-  <si>
-    <t>mercado</t>
-  </si>
-  <si>
-    <t>mer</t>
-  </si>
-  <si>
-    <t>SPORT, WORKSHOP</t>
-  </si>
-  <si>
-    <t>stanton</t>
-  </si>
-  <si>
-    <t>sta</t>
-  </si>
-  <si>
-    <t>russell</t>
-  </si>
-  <si>
-    <t>rus</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Teaching Subjects Ids</t>
-  </si>
-  <si>
-    <t>Teaching Subjects Symbols</t>
-  </si>
-  <si>
-    <t>Jill Patterson</t>
-  </si>
-  <si>
-    <t>JP</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Christopher Cochran</t>
-  </si>
-  <si>
-    <t>16, 19, 8</t>
-  </si>
-  <si>
-    <t>medtmc, medt3d, eng</t>
-  </si>
-  <si>
-    <t>Shane Allen</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Austin Burton</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>19, 14, 9</t>
-  </si>
-  <si>
-    <t>medt3d, rel, geo</t>
-  </si>
-  <si>
-    <t>Sean Burnett</t>
-  </si>
-  <si>
-    <t>Abigail Sullivan</t>
-  </si>
-  <si>
-    <t>8, 2</t>
-  </si>
-  <si>
-    <t>eng, nwp</t>
-  </si>
-  <si>
-    <t>Teresa Baker</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>2, 17</t>
-  </si>
-  <si>
-    <t>nwp, medtfi</t>
-  </si>
-  <si>
-    <t>James Wood</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Monique Ware</t>
-  </si>
-  <si>
-    <t>19, 15, 7</t>
-  </si>
-  <si>
-    <t>medt3d, medtpd, wt</t>
-  </si>
-  <si>
-    <t>Sarah Rivera</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>2, 13, 14</t>
-  </si>
-  <si>
-    <t>nwp, itp, rel</t>
-  </si>
-  <si>
-    <t>Samantha Larson</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scott Duffy</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Andrew Jackson</t>
-  </si>
-  <si>
-    <t>AJ</t>
-  </si>
-  <si>
-    <t>Michael Mckinney</t>
-  </si>
-  <si>
-    <t>MM</t>
-  </si>
-  <si>
-    <t>19, 4, 5</t>
-  </si>
-  <si>
-    <t>medt3d, bio, nwc</t>
-  </si>
-  <si>
-    <t>Brian Wood</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Steven Martinez</t>
-  </si>
-  <si>
-    <t>5, 1</t>
-  </si>
-  <si>
-    <t>nwc, am</t>
-  </si>
-  <si>
-    <t>Jordan Fletcher</t>
-  </si>
-  <si>
-    <t>14, 15, 9</t>
-  </si>
-  <si>
-    <t>rel, medtpd, geo</t>
-  </si>
-  <si>
-    <t>Riley Gutierrez</t>
-  </si>
-  <si>
-    <t>RG</t>
-  </si>
-  <si>
-    <t>4, 8, 3</t>
-  </si>
-  <si>
-    <t>bio, eng, ges</t>
-  </si>
-  <si>
-    <t>Nathan King</t>
-  </si>
-  <si>
     <t>5, 17</t>
   </si>
   <si>
-    <t>nwc, medtfi</t>
-  </si>
-  <si>
     <t>Jake Kelley</t>
   </si>
   <si>
@@ -490,9 +475,6 @@
   </si>
   <si>
     <t>13, 3, 17</t>
-  </si>
-  <si>
-    <t>itp, ges, medtfi</t>
   </si>
 </sst>
 </file>
@@ -537,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -601,7 +583,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -689,7 +671,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="17">
@@ -705,7 +687,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="19">
@@ -721,7 +703,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="21">
@@ -729,7 +711,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="22">
@@ -737,6 +719,22 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="n" s="0">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="B23" t="n" s="0">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="B24" t="n" s="0">
         <v>14.0</v>
       </c>
     </row>
@@ -747,7 +745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -769,12 +767,6 @@
       <c r="F1" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="G1" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>15</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
@@ -784,21 +776,15 @@
         <v>8.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>11.0</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="F2" t="n" s="0">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
         <v>2.0</v>
       </c>
-      <c r="G2" t="b" s="0">
+      <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" t="b" s="0">
+      <c r="F2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -810,21 +796,15 @@
         <v>12.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="D3" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="F3" t="n" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n">
         <v>2.0</v>
       </c>
-      <c r="G3" t="b" s="0">
+      <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" t="b" s="0">
+      <c r="F3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -836,21 +816,15 @@
         <v>1.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D4" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="F4" t="n" s="0">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
         <v>3.0</v>
       </c>
-      <c r="G4" t="b" s="0">
+      <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="b" s="0">
+      <c r="F4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -862,21 +836,15 @@
         <v>6.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="F5" t="n" s="0">
+        <v>17</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.0</v>
       </c>
-      <c r="G5" t="b" s="0">
+      <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="b" s="0">
+      <c r="F5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -888,21 +856,15 @@
         <v>17.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D6" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="F6" t="n" s="0">
+        <v>18</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.0</v>
       </c>
-      <c r="G6" t="b" s="0">
+      <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="b" s="0">
+      <c r="F6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -914,21 +876,15 @@
         <v>9.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D7" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="F7" t="n" s="0">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
         <v>2.0</v>
       </c>
-      <c r="G7" t="b" s="0">
+      <c r="E7" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="b" s="0">
+      <c r="F7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -940,21 +896,15 @@
         <v>9.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D8" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="F8" t="n" s="0">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.0</v>
       </c>
-      <c r="G8" t="b" s="0">
+      <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="b" s="0">
+      <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -966,21 +916,15 @@
         <v>8.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D9" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F9" t="n" s="0">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
         <v>3.0</v>
       </c>
-      <c r="G9" t="b" s="0">
+      <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="b" s="0">
+      <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -992,21 +936,15 @@
         <v>8.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D10" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="F10" t="n" s="0">
+        <v>21</v>
+      </c>
+      <c r="D10" t="n">
         <v>2.0</v>
       </c>
-      <c r="G10" t="b" s="0">
+      <c r="E10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="b" s="0">
+      <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1020,19 +958,13 @@
       <c r="C11" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="D11" t="n" s="0">
-        <v>9.0</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="F11" t="n" s="0">
+      <c r="D11" t="n">
         <v>2.0</v>
       </c>
-      <c r="G11" t="b" s="0">
+      <c r="E11" t="b">
         <v>0</v>
       </c>
-      <c r="H11" t="b" s="0">
+      <c r="F11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1044,21 +976,15 @@
         <v>19.0</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="D12" t="n" s="0">
-        <v>19.0</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="F12" t="n" s="0">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
         <v>2.0</v>
       </c>
-      <c r="G12" t="b" s="0">
+      <c r="E12" t="b">
         <v>0</v>
       </c>
-      <c r="H12" t="b" s="0">
+      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1070,21 +996,15 @@
         <v>10.0</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="D13" t="n" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F13" t="n" s="0">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
         <v>3.0</v>
       </c>
-      <c r="G13" t="b" s="0">
+      <c r="E13" t="b">
         <v>0</v>
       </c>
-      <c r="H13" t="b" s="0">
+      <c r="F13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1096,21 +1016,15 @@
         <v>5.0</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="D14" t="n" s="0">
-        <v>12.0</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="F14" t="n" s="0">
+        <v>25</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.0</v>
       </c>
-      <c r="G14" t="b" s="0">
+      <c r="E14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="b" s="0">
+      <c r="F14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1122,21 +1036,15 @@
         <v>3.0</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="D15" t="n" s="0">
-        <v>17.0</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="F15" t="n" s="0">
+        <v>21</v>
+      </c>
+      <c r="D15" t="n">
         <v>3.0</v>
       </c>
-      <c r="G15" t="b" s="0">
+      <c r="E15" t="b">
         <v>0</v>
       </c>
-      <c r="H15" t="b" s="0">
+      <c r="F15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1155,13 +1063,13 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -1169,13 +1077,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -1183,13 +1091,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -1197,13 +1105,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -1211,13 +1119,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -1225,13 +1133,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -1239,13 +1147,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -1253,13 +1161,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1267,13 +1175,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -1281,13 +1189,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11">
@@ -1295,13 +1203,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -1309,13 +1217,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1323,13 +1231,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -1337,13 +1245,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -1351,13 +1259,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -1365,13 +1273,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1379,13 +1287,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
@@ -1393,13 +1301,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -1407,13 +1315,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -1421,13 +1329,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="D20" t="s" s="0">
         <v>31</v>
-      </c>
-      <c r="D20" t="s" s="0">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1445,16 +1353,16 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s" s="0">
         <v>71</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -1465,13 +1373,13 @@
         <v>66.0</v>
       </c>
       <c r="C2" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>74</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>75</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -1482,13 +1390,13 @@
         <v>480.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -1499,13 +1407,13 @@
         <v>447.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -1516,13 +1424,13 @@
         <v>256.0</v>
       </c>
       <c r="C5" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>81</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -1533,13 +1441,13 @@
         <v>313.0</v>
       </c>
       <c r="C6" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>84</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -1550,13 +1458,13 @@
         <v>421.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -1567,13 +1475,13 @@
         <v>323.0</v>
       </c>
       <c r="C8" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>88</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -1584,13 +1492,13 @@
         <v>398.0</v>
       </c>
       <c r="C9" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="E9" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="D9" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -1601,13 +1509,13 @@
         <v>488.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -1618,13 +1526,13 @@
         <v>125.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1634,24 +1542,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
@@ -1659,16 +1564,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1676,16 +1578,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -1693,16 +1592,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
@@ -1710,16 +1606,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>111</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
@@ -1727,16 +1620,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -1744,16 +1634,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>115</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
@@ -1761,16 +1648,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>119</v>
-      </c>
-      <c r="E8" t="s" s="0">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
@@ -1778,16 +1662,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s" s="0">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -1795,16 +1676,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -1812,16 +1690,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="E11" t="s" s="0">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12">
@@ -1829,16 +1704,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="E12" t="s" s="0">
-        <v>33</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1846,16 +1718,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s" s="0">
-        <v>64</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -1863,16 +1732,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="E14" t="s" s="0">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1880,16 +1746,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="E15" t="s" s="0">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16">
@@ -1897,16 +1760,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="E16" t="s" s="0">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17">
@@ -1914,16 +1774,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>143</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">
@@ -1931,16 +1788,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
@@ -1948,16 +1802,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="E19" t="s" s="0">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
@@ -1965,16 +1816,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>153</v>
-      </c>
-      <c r="E20" t="s" s="0">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
@@ -1982,16 +1830,13 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>157</v>
-      </c>
-      <c r="E21" t="s" s="0">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="159">
   <si>
     <t>CSI Id</t>
   </si>
@@ -48,7 +48,13 @@
     <t>Subject Id</t>
   </si>
   <si>
-    <t>Teacher Ids</t>
+    <t>Subject Symbol</t>
+  </si>
+  <si>
+    <t>Teacher Id</t>
+  </si>
+  <si>
+    <t>Teacher Symbol</t>
   </si>
   <si>
     <t>Weekly Hours</t>
@@ -60,354 +66,360 @@
     <t>Is better as Double Period</t>
   </si>
   <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>insy</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>recht</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>medtfi</t>
+  </si>
+  <si>
+    <t>JW</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>JF</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>medt3d</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>sew</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>nwc</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>ges</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Required Room Types</t>
+  </si>
+  <si>
+    <t>angewandte mathematik</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>naturwissenschaften physik</t>
+  </si>
+  <si>
+    <t>nwp</t>
+  </si>
+  <si>
+    <t>PHY</t>
+  </si>
+  <si>
+    <t>geschichte</t>
+  </si>
+  <si>
+    <t>biologie</t>
+  </si>
+  <si>
+    <t>bio</t>
+  </si>
+  <si>
+    <t>naturwissenschaften chemie</t>
+  </si>
+  <si>
+    <t>CHEM, PHY</t>
+  </si>
+  <si>
+    <t>wirtschaft</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>englisch</t>
+  </si>
+  <si>
+    <t>geographie</t>
+  </si>
+  <si>
+    <t>software entwicklung</t>
+  </si>
+  <si>
+    <t>deutsch</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>informationssysteme</t>
+  </si>
+  <si>
+    <t>informationstechnische projekte</t>
+  </si>
+  <si>
+    <t>itp</t>
+  </si>
+  <si>
+    <t>religion</t>
+  </si>
+  <si>
+    <t>rel</t>
+  </si>
+  <si>
+    <t>medientechnik print und design</t>
+  </si>
+  <si>
+    <t>medtpd</t>
+  </si>
+  <si>
+    <t>medientechnik mobile computing</t>
+  </si>
+  <si>
+    <t>medtmc</t>
+  </si>
+  <si>
+    <t>medientechnik film und audio</t>
+  </si>
+  <si>
+    <t>medientechnik social media</t>
+  </si>
+  <si>
+    <t>medtsm</t>
+  </si>
+  <si>
+    <t>medientechnik virtuelle welten und spieleentwicklung</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Room Type</t>
+  </si>
+  <si>
+    <t>potts</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>WORKSHOP</t>
+  </si>
+  <si>
+    <t>vincent</t>
+  </si>
+  <si>
+    <t>vin</t>
+  </si>
+  <si>
+    <t>williams</t>
+  </si>
+  <si>
+    <t>wil</t>
+  </si>
+  <si>
+    <t>morgan</t>
+  </si>
+  <si>
+    <t>mor</t>
+  </si>
+  <si>
+    <t>WORKSHOP, CLASSROOM</t>
+  </si>
+  <si>
+    <t>hernandez</t>
+  </si>
+  <si>
+    <t>her</t>
+  </si>
+  <si>
+    <t>SPORT, EDV</t>
+  </si>
+  <si>
+    <t>CLASSROOM, WORKSHOP</t>
+  </si>
+  <si>
+    <t>cervantes</t>
+  </si>
+  <si>
+    <t>cer</t>
+  </si>
+  <si>
+    <t>SPORT</t>
+  </si>
+  <si>
+    <t>mercado</t>
+  </si>
+  <si>
+    <t>mer</t>
+  </si>
+  <si>
+    <t>SPORT, WORKSHOP</t>
+  </si>
+  <si>
+    <t>stanton</t>
+  </si>
+  <si>
+    <t>sta</t>
+  </si>
+  <si>
+    <t>russell</t>
+  </si>
+  <si>
+    <t>rus</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Teaching Subjects Ids</t>
+  </si>
+  <si>
+    <t>Teaching Subjects Symbols</t>
+  </si>
+  <si>
+    <t>Jill Patterson</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
     <t>11</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>Christopher Cochran</t>
+  </si>
+  <si>
+    <t>16, 19, 8</t>
+  </si>
+  <si>
+    <t>medtmc, medt3d, eng</t>
+  </si>
+  <si>
+    <t>Shane Allen</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Austin Burton</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>19, 14, 9</t>
+  </si>
+  <si>
+    <t>medt3d, rel, geo</t>
+  </si>
+  <si>
+    <t>Sean Burnett</t>
+  </si>
+  <si>
+    <t>Abigail Sullivan</t>
+  </si>
+  <si>
+    <t>8, 2</t>
+  </si>
+  <si>
+    <t>eng, nwp</t>
+  </si>
+  <si>
+    <t>Teresa Baker</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>2, 17</t>
+  </si>
+  <si>
+    <t>nwp, medtfi</t>
+  </si>
+  <si>
+    <t>James Wood</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
+    <t>Monique Ware</t>
+  </si>
+  <si>
+    <t>19, 15, 7</t>
+  </si>
+  <si>
+    <t>medt3d, medtpd, wt</t>
+  </si>
+  <si>
+    <t>Sarah Rivera</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>2, 13, 14</t>
+  </si>
+  <si>
+    <t>nwp, itp, rel</t>
+  </si>
+  <si>
+    <t>Samantha Larson</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scott Duffy</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Symbol</t>
-  </si>
-  <si>
-    <t>Required Room Types</t>
-  </si>
-  <si>
-    <t>angewandte mathematik</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>naturwissenschaften physik</t>
-  </si>
-  <si>
-    <t>nwp</t>
-  </si>
-  <si>
-    <t>PHY</t>
-  </si>
-  <si>
-    <t>geschichte</t>
-  </si>
-  <si>
-    <t>ges</t>
-  </si>
-  <si>
-    <t>biologie</t>
-  </si>
-  <si>
-    <t>bio</t>
-  </si>
-  <si>
-    <t>naturwissenschaften chemie</t>
-  </si>
-  <si>
-    <t>nwc</t>
-  </si>
-  <si>
-    <t>CHEM, PHY</t>
-  </si>
-  <si>
-    <t>recht</t>
-  </si>
-  <si>
-    <t>wirtschaft</t>
-  </si>
-  <si>
-    <t>wt</t>
-  </si>
-  <si>
-    <t>englisch</t>
-  </si>
-  <si>
-    <t>eng</t>
-  </si>
-  <si>
-    <t>geographie</t>
-  </si>
-  <si>
-    <t>geo</t>
-  </si>
-  <si>
-    <t>software entwicklung</t>
-  </si>
-  <si>
-    <t>sew</t>
-  </si>
-  <si>
-    <t>deutsch</t>
-  </si>
-  <si>
-    <t>de</t>
-  </si>
-  <si>
-    <t>informationssysteme</t>
-  </si>
-  <si>
-    <t>insy</t>
-  </si>
-  <si>
-    <t>informationstechnische projekte</t>
-  </si>
-  <si>
-    <t>itp</t>
-  </si>
-  <si>
-    <t>religion</t>
-  </si>
-  <si>
-    <t>rel</t>
-  </si>
-  <si>
-    <t>medientechnik print und design</t>
-  </si>
-  <si>
-    <t>medtpd</t>
-  </si>
-  <si>
-    <t>medientechnik mobile computing</t>
-  </si>
-  <si>
-    <t>medtmc</t>
-  </si>
-  <si>
-    <t>medientechnik film und audio</t>
-  </si>
-  <si>
-    <t>medtfi</t>
-  </si>
-  <si>
-    <t>medientechnik social media</t>
-  </si>
-  <si>
-    <t>medtsm</t>
-  </si>
-  <si>
-    <t>medientechnik virtuelle welten und spieleentwicklung</t>
-  </si>
-  <si>
-    <t>medt3d</t>
-  </si>
-  <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Room Type</t>
-  </si>
-  <si>
-    <t>potts</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>WORKSHOP</t>
-  </si>
-  <si>
-    <t>vincent</t>
-  </si>
-  <si>
-    <t>vin</t>
-  </si>
-  <si>
-    <t>williams</t>
-  </si>
-  <si>
-    <t>wil</t>
-  </si>
-  <si>
-    <t>morgan</t>
-  </si>
-  <si>
-    <t>mor</t>
-  </si>
-  <si>
-    <t>WORKSHOP, CLASSROOM</t>
-  </si>
-  <si>
-    <t>hernandez</t>
-  </si>
-  <si>
-    <t>her</t>
-  </si>
-  <si>
-    <t>SPORT, EDV</t>
-  </si>
-  <si>
-    <t>CLASSROOM, WORKSHOP</t>
-  </si>
-  <si>
-    <t>cervantes</t>
-  </si>
-  <si>
-    <t>cer</t>
-  </si>
-  <si>
-    <t>SPORT</t>
-  </si>
-  <si>
-    <t>mercado</t>
-  </si>
-  <si>
-    <t>mer</t>
-  </si>
-  <si>
-    <t>SPORT, WORKSHOP</t>
-  </si>
-  <si>
-    <t>stanton</t>
-  </si>
-  <si>
-    <t>sta</t>
-  </si>
-  <si>
-    <t>russell</t>
-  </si>
-  <si>
-    <t>rus</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Teaching Subjects Ids</t>
-  </si>
-  <si>
-    <t>Jill Patterson</t>
-  </si>
-  <si>
-    <t>JP</t>
-  </si>
-  <si>
-    <t>Christopher Cochran</t>
-  </si>
-  <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>16, 19, 8</t>
-  </si>
-  <si>
-    <t>Shane Allen</t>
-  </si>
-  <si>
-    <t>SA</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Austin Burton</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>19, 14, 9</t>
-  </si>
-  <si>
-    <t>Sean Burnett</t>
-  </si>
-  <si>
-    <t>SB</t>
-  </si>
-  <si>
-    <t>Abigail Sullivan</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>8, 2</t>
-  </si>
-  <si>
-    <t>Teresa Baker</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>2, 17</t>
-  </si>
-  <si>
-    <t>James Wood</t>
-  </si>
-  <si>
-    <t>JW</t>
-  </si>
-  <si>
-    <t>Monique Ware</t>
-  </si>
-  <si>
-    <t>MW</t>
-  </si>
-  <si>
-    <t>19, 15, 7</t>
-  </si>
-  <si>
-    <t>Sarah Rivera</t>
-  </si>
-  <si>
-    <t>SR</t>
-  </si>
-  <si>
-    <t>2, 13, 14</t>
-  </si>
-  <si>
-    <t>Samantha Larson</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Scott Duffy</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>Andrew Jackson</t>
   </si>
   <si>
@@ -423,33 +435,33 @@
     <t>19, 4, 5</t>
   </si>
   <si>
+    <t>medt3d, bio, nwc</t>
+  </si>
+  <si>
     <t>Brian Wood</t>
   </si>
   <si>
-    <t>BW</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
     <t>Steven Martinez</t>
   </si>
   <si>
-    <t>SM</t>
-  </si>
-  <si>
     <t>5, 1</t>
   </si>
   <si>
+    <t>nwc, am</t>
+  </si>
+  <si>
     <t>Jordan Fletcher</t>
   </si>
   <si>
-    <t>JF</t>
-  </si>
-  <si>
     <t>14, 15, 9</t>
   </si>
   <si>
+    <t>rel, medtpd, geo</t>
+  </si>
+  <si>
     <t>Riley Gutierrez</t>
   </si>
   <si>
@@ -459,15 +471,18 @@
     <t>4, 8, 3</t>
   </si>
   <si>
+    <t>bio, eng, ges</t>
+  </si>
+  <si>
     <t>Nathan King</t>
   </si>
   <si>
-    <t>NK</t>
-  </si>
-  <si>
     <t>5, 17</t>
   </si>
   <si>
+    <t>nwc, medtfi</t>
+  </si>
+  <si>
     <t>Jake Kelley</t>
   </si>
   <si>
@@ -475,6 +490,9 @@
   </si>
   <si>
     <t>13, 3, 17</t>
+  </si>
+  <si>
+    <t>itp, ges, medtfi</t>
   </si>
 </sst>
 </file>
@@ -519,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -583,7 +601,7 @@
         <v>3.0</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
@@ -671,7 +689,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="17">
@@ -687,7 +705,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="19">
@@ -703,7 +721,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="21">
@@ -711,7 +729,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="22">
@@ -719,22 +737,6 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n" s="0">
-        <v>21.0</v>
-      </c>
-      <c r="B23" t="n" s="0">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n" s="0">
-        <v>22.0</v>
-      </c>
-      <c r="B24" t="n" s="0">
         <v>14.0</v>
       </c>
     </row>
@@ -745,7 +747,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -767,6 +769,12 @@
       <c r="F1" t="s" s="0">
         <v>13</v>
       </c>
+      <c r="G1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
@@ -776,15 +784,21 @@
         <v>8.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D2" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F2" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E2" t="b">
+      <c r="G2" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F2" t="b">
+      <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -796,15 +810,21 @@
         <v>12.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E3" t="b">
+      <c r="G3" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F3" t="b">
+      <c r="H3" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -816,15 +836,21 @@
         <v>1.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="F4" t="n" s="0">
         <v>3.0</v>
       </c>
-      <c r="E4" t="b">
+      <c r="G4" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F4" t="b">
+      <c r="H4" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -836,15 +862,21 @@
         <v>6.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F5" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E5" t="b">
+      <c r="G5" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="F5" t="b">
+      <c r="H5" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -856,15 +888,21 @@
         <v>17.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="D6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E6" t="b">
+      <c r="G6" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F6" t="b">
+      <c r="H6" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -876,15 +914,21 @@
         <v>9.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="F7" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E7" t="b">
+      <c r="G7" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="F7" t="b">
+      <c r="H7" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -896,15 +940,21 @@
         <v>9.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="D8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F8" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E8" t="b">
+      <c r="G8" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F8" t="b">
+      <c r="H8" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -916,15 +966,21 @@
         <v>8.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n" s="0">
         <v>3.0</v>
       </c>
-      <c r="E9" t="b">
+      <c r="G9" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F9" t="b">
+      <c r="H9" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -936,15 +992,21 @@
         <v>8.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F10" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E10" t="b">
+      <c r="G10" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F10" t="b">
+      <c r="H10" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -958,13 +1020,19 @@
       <c r="C11" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E11" t="b">
+      <c r="G11" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="F11" t="b">
+      <c r="H11" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -976,15 +1044,21 @@
         <v>19.0</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="D12" t="n">
+        <v>31</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F12" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="E12" t="b">
+      <c r="G12" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="F12" t="b">
+      <c r="H12" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -996,15 +1070,21 @@
         <v>10.0</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="D13" t="n">
+        <v>33</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F13" t="n" s="0">
         <v>3.0</v>
       </c>
-      <c r="E13" t="b">
+      <c r="G13" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="F13" t="b">
+      <c r="H13" t="b" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1016,15 +1096,21 @@
         <v>5.0</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F14" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E14" t="b">
+      <c r="G14" t="b" s="0">
         <v>1</v>
       </c>
-      <c r="F14" t="b">
+      <c r="H14" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1036,15 +1122,21 @@
         <v>3.0</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="D15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F15" t="n" s="0">
         <v>3.0</v>
       </c>
-      <c r="E15" t="b">
+      <c r="G15" t="b" s="0">
         <v>0</v>
       </c>
-      <c r="F15" t="b">
+      <c r="H15" t="b" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1063,13 +1155,13 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1077,13 +1169,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -1091,13 +1183,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -1105,13 +1197,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -1119,13 +1211,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -1133,13 +1225,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1147,13 +1239,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>42</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -1161,13 +1253,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9">
@@ -1175,13 +1267,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1281,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -1203,13 +1295,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -1217,13 +1309,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -1231,13 +1323,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -1245,13 +1337,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -1259,13 +1351,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -1273,13 +1365,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -1287,13 +1379,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -1301,13 +1393,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -1315,13 +1407,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -1329,13 +1421,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1353,16 +1445,16 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -1373,13 +1465,13 @@
         <v>66.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -1390,13 +1482,13 @@
         <v>480.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>76</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -1407,13 +1499,13 @@
         <v>447.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1424,13 +1516,13 @@
         <v>256.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -1441,13 +1533,13 @@
         <v>313.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -1458,13 +1550,13 @@
         <v>421.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -1475,13 +1567,13 @@
         <v>323.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1584,13 @@
         <v>398.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -1509,13 +1601,13 @@
         <v>488.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -1526,13 +1618,13 @@
         <v>125.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1542,21 +1634,24 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>100</v>
       </c>
     </row>
     <row r="2">
@@ -1564,13 +1659,16 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>14</v>
+        <v>103</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -1578,13 +1676,16 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>102</v>
+        <v>105</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>106</v>
       </c>
     </row>
     <row r="4">
@@ -1592,13 +1693,16 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1606,13 +1710,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>108</v>
+        <v>111</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>112</v>
       </c>
     </row>
     <row r="6">
@@ -1620,13 +1727,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>14</v>
+        <v>103</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1634,13 +1744,16 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>113</v>
+        <v>115</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>116</v>
       </c>
     </row>
     <row r="8">
@@ -1648,13 +1761,16 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>116</v>
+        <v>119</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -1662,13 +1778,16 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>23</v>
+        <v>122</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -1676,13 +1795,16 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>121</v>
+        <v>124</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>125</v>
       </c>
     </row>
     <row r="11">
@@ -1690,13 +1812,16 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -1704,13 +1829,16 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>127</v>
+        <v>131</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -1718,13 +1846,16 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>24</v>
+        <v>133</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -1732,13 +1863,16 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>14</v>
+        <v>103</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -1746,13 +1880,16 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>134</v>
+        <v>138</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>139</v>
       </c>
     </row>
     <row r="16">
@@ -1760,13 +1897,16 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>137</v>
+        <v>141</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>48</v>
       </c>
     </row>
     <row r="17">
@@ -1774,13 +1914,16 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>140</v>
+        <v>143</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>144</v>
       </c>
     </row>
     <row r="18">
@@ -1788,13 +1931,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>143</v>
+        <v>146</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>147</v>
       </c>
     </row>
     <row r="19">
@@ -1802,13 +1948,16 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>146</v>
+        <v>150</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>151</v>
       </c>
     </row>
     <row r="20">
@@ -1816,13 +1965,16 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>154</v>
       </c>
     </row>
     <row r="21">
@@ -1830,13 +1982,16 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>152</v>
+        <v>157</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -575,7 +575,7 @@
         <v>2.0</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="5">
@@ -599,7 +599,7 @@
         <v>5.0</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="10">
@@ -623,7 +623,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         <v>9.0</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="12">
@@ -639,7 +639,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="13">
@@ -647,7 +647,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>12.0</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="15">
@@ -663,7 +663,7 @@
         <v>13.0</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="16">
@@ -671,7 +671,7 @@
         <v>14.0</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="17">
@@ -679,7 +679,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="18">
@@ -695,7 +695,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="20">

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="154">
   <si>
     <t>CSI Id</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Teacher Ids</t>
+  </si>
+  <si>
+    <t>School class ID</t>
   </si>
   <si>
     <t>Weekly Hours</t>
@@ -519,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -591,7 +594,7 @@
         <v>4.0</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
@@ -607,7 +610,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +618,7 @@
         <v>7.0</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="10">
@@ -623,7 +626,7 @@
         <v>8.0</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="11">
@@ -639,7 +642,7 @@
         <v>10.0</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="13">
@@ -647,7 +650,7 @@
         <v>11.0</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="14">
@@ -663,7 +666,7 @@
         <v>13.0</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="16">
@@ -679,7 +682,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="18">
@@ -687,7 +690,7 @@
         <v>16.0</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="19">
@@ -695,7 +698,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="20">
@@ -703,7 +706,7 @@
         <v>18.0</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="21">
@@ -719,7 +722,7 @@
         <v>20.0</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="23">
@@ -727,7 +730,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="24">
@@ -735,6 +738,14 @@
         <v>22.0</v>
       </c>
       <c r="B24" t="n" s="0">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="B25" t="n" s="0">
         <v>14.0</v>
       </c>
     </row>
@@ -745,7 +756,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -767,6 +778,9 @@
       <c r="F1" t="s" s="0">
         <v>13</v>
       </c>
+      <c r="G1" t="s" s="0">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
@@ -776,15 +790,18 @@
         <v>8.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="n">
         <v>2.0</v>
       </c>
-      <c r="E2" t="b">
+      <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="b">
+      <c r="G2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -796,15 +813,18 @@
         <v>12.0</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="n">
         <v>2.0</v>
       </c>
-      <c r="E3" t="b">
+      <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="b">
+      <c r="G3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -816,15 +836,18 @@
         <v>1.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="n">
         <v>3.0</v>
       </c>
-      <c r="E4" t="b">
+      <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="b">
+      <c r="G4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -836,15 +859,18 @@
         <v>6.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>1.0</v>
       </c>
-      <c r="E5" t="b">
+      <c r="E5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="b">
+      <c r="G5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -856,15 +882,18 @@
         <v>17.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
         <v>1.0</v>
       </c>
-      <c r="E6" t="b">
+      <c r="E6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="b">
+      <c r="G6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -876,15 +905,18 @@
         <v>9.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="n">
         <v>2.0</v>
       </c>
-      <c r="E7" t="b">
+      <c r="F7" t="b">
         <v>0</v>
       </c>
-      <c r="F7" t="b">
+      <c r="G7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -896,15 +928,18 @@
         <v>9.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
         <v>1.0</v>
       </c>
-      <c r="E8" t="b">
+      <c r="E8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" t="b">
+      <c r="G8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -916,15 +951,18 @@
         <v>8.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="n">
         <v>3.0</v>
       </c>
-      <c r="E9" t="b">
+      <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="F9" t="b">
+      <c r="G9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -936,15 +974,18 @@
         <v>8.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="n">
         <v>2.0</v>
       </c>
-      <c r="E10" t="b">
+      <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="F10" t="b">
+      <c r="G10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -956,15 +997,18 @@
         <v>6.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.0</v>
       </c>
-      <c r="E11" t="b">
+      <c r="F11" t="b">
         <v>0</v>
       </c>
-      <c r="F11" t="b">
+      <c r="G11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -976,15 +1020,18 @@
         <v>19.0</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="n">
         <v>2.0</v>
       </c>
-      <c r="E12" t="b">
+      <c r="F12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" t="b">
+      <c r="G12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -996,15 +1043,18 @@
         <v>10.0</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E13" t="n">
         <v>3.0</v>
       </c>
-      <c r="E13" t="b">
+      <c r="F13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" t="b">
+      <c r="G13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1016,15 +1066,18 @@
         <v>5.0</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
         <v>1.0</v>
       </c>
-      <c r="E14" t="b">
+      <c r="E14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="b">
         <v>1</v>
       </c>
-      <c r="F14" t="b">
+      <c r="G14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1036,15 +1089,18 @@
         <v>3.0</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E15" t="n">
         <v>3.0</v>
       </c>
-      <c r="E15" t="b">
+      <c r="F15" t="b">
         <v>0</v>
       </c>
-      <c r="F15" t="b">
+      <c r="G15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1063,13 +1119,13 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
@@ -1077,13 +1133,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -1091,13 +1147,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -1105,13 +1161,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -1119,13 +1175,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -1133,13 +1189,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -1147,13 +1203,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -1161,13 +1217,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -1175,13 +1231,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1245,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -1203,13 +1259,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -1217,13 +1273,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -1231,13 +1287,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -1245,13 +1301,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -1259,13 +1315,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -1273,13 +1329,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1287,13 +1343,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -1301,13 +1357,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -1315,13 +1371,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
@@ -1329,13 +1385,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1353,16 +1409,16 @@
         <v>8</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -1373,13 +1429,13 @@
         <v>66.0</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -1390,13 +1446,13 @@
         <v>480.0</v>
       </c>
       <c r="C3" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>75</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>76</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -1407,13 +1463,13 @@
         <v>447.0</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -1424,13 +1480,13 @@
         <v>256.0</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -1441,13 +1497,13 @@
         <v>313.0</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -1458,13 +1514,13 @@
         <v>421.0</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -1475,13 +1531,13 @@
         <v>323.0</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1548,13 @@
         <v>398.0</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -1509,13 +1565,13 @@
         <v>488.0</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -1526,13 +1582,13 @@
         <v>125.0</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1547,16 +1603,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
@@ -1564,13 +1620,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1578,13 +1634,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4">
@@ -1592,13 +1648,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -1606,13 +1662,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
@@ -1620,13 +1676,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1634,13 +1690,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -1648,13 +1704,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
@@ -1662,13 +1718,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -1676,13 +1732,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -1690,13 +1746,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
@@ -1704,13 +1760,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1718,13 +1774,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -1732,13 +1788,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1746,13 +1802,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
@@ -1760,13 +1816,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -1774,13 +1830,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18">
@@ -1788,13 +1844,13 @@
         <v>17.0</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
@@ -1802,13 +1858,13 @@
         <v>18.0</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s" s="0">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20">
@@ -1816,13 +1872,13 @@
         <v>19.0</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D20" t="s" s="0">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
@@ -1830,13 +1886,13 @@
         <v>20.0</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s" s="0">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/leo-planer/src/files/excelFiles/export/test1.xlsx
+++ b/leo-planer/src/files/excelFiles/export/test1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="158">
   <si>
     <t>ID</t>
   </si>
@@ -30,6 +30,126 @@
     <t>Required Room Types</t>
   </si>
   <si>
+    <t>angewandte mathematik</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>naturwissenschaften physik</t>
+  </si>
+  <si>
+    <t>nwp</t>
+  </si>
+  <si>
+    <t>PHY</t>
+  </si>
+  <si>
+    <t>geschichte</t>
+  </si>
+  <si>
+    <t>ges</t>
+  </si>
+  <si>
+    <t>biologie</t>
+  </si>
+  <si>
+    <t>bio</t>
+  </si>
+  <si>
+    <t>naturwissenschaften chemie</t>
+  </si>
+  <si>
+    <t>nwc</t>
+  </si>
+  <si>
+    <t>CHEM, PHY</t>
+  </si>
+  <si>
+    <t>recht</t>
+  </si>
+  <si>
+    <t>wirtschaft</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>englisch</t>
+  </si>
+  <si>
+    <t>eng</t>
+  </si>
+  <si>
+    <t>geographie</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>software entwicklung</t>
+  </si>
+  <si>
+    <t>sew</t>
+  </si>
+  <si>
+    <t>deutsch</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>informationssysteme</t>
+  </si>
+  <si>
+    <t>insy</t>
+  </si>
+  <si>
+    <t>informationstechnische projekte</t>
+  </si>
+  <si>
+    <t>itp</t>
+  </si>
+  <si>
+    <t>religion</t>
+  </si>
+  <si>
+    <t>rel</t>
+  </si>
+  <si>
+    <t>medientechnik print und design</t>
+  </si>
+  <si>
+    <t>medtpd</t>
+  </si>
+  <si>
+    <t>medientechnik mobile computing</t>
+  </si>
+  <si>
+    <t>medtmc</t>
+  </si>
+  <si>
+    <t>medientechnik film und audio</t>
+  </si>
+  <si>
+    <t>medtfi</t>
+  </si>
+  <si>
+    <t>medientechnik social media</t>
+  </si>
+  <si>
+    <t>medtsm</t>
+  </si>
+  <si>
+    <t>medientechnik virtuelle welten und spieleentwicklung</t>
+  </si>
+  <si>
+    <t>medt3d</t>
+  </si>
+  <si>
     <t>Number</t>
   </si>
   <si>
@@ -39,15 +159,279 @@
     <t>Room Type</t>
   </si>
   <si>
+    <t>potts</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>WORKSHOP</t>
+  </si>
+  <si>
+    <t>vincent</t>
+  </si>
+  <si>
+    <t>vin</t>
+  </si>
+  <si>
+    <t>williams</t>
+  </si>
+  <si>
+    <t>wil</t>
+  </si>
+  <si>
+    <t>morgan</t>
+  </si>
+  <si>
+    <t>mor</t>
+  </si>
+  <si>
+    <t>WORKSHOP, CLASSROOM</t>
+  </si>
+  <si>
+    <t>hernandez</t>
+  </si>
+  <si>
+    <t>her</t>
+  </si>
+  <si>
+    <t>SPORT, EDV</t>
+  </si>
+  <si>
+    <t>CLASSROOM, WORKSHOP</t>
+  </si>
+  <si>
+    <t>cervantes</t>
+  </si>
+  <si>
+    <t>cer</t>
+  </si>
+  <si>
+    <t>SPORT</t>
+  </si>
+  <si>
+    <t>mercado</t>
+  </si>
+  <si>
+    <t>mer</t>
+  </si>
+  <si>
+    <t>SPORT, WORKSHOP</t>
+  </si>
+  <si>
+    <t>stanton</t>
+  </si>
+  <si>
+    <t>sta</t>
+  </si>
+  <si>
+    <t>russell</t>
+  </si>
+  <si>
+    <t>rus</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
     <t>Teaching Subjects Ids</t>
   </si>
   <si>
+    <t>Jill Patterson</t>
+  </si>
+  <si>
+    <t>JP</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Christopher Cochran</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>16, 19, 8</t>
+  </si>
+  <si>
+    <t>Shane Allen</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Austin Burton</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>19, 14, 9</t>
+  </si>
+  <si>
+    <t>Sean Burnett</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>Abigail Sullivan</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>8, 2</t>
+  </si>
+  <si>
+    <t>Teresa Baker</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>2, 17</t>
+  </si>
+  <si>
+    <t>James Wood</t>
+  </si>
+  <si>
+    <t>JW</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Monique Ware</t>
+  </si>
+  <si>
+    <t>MW</t>
+  </si>
+  <si>
+    <t>19, 15, 7</t>
+  </si>
+  <si>
+    <t>Sarah Rivera</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
+  <si>
+    <t>2, 13, 14</t>
+  </si>
+  <si>
+    <t>Samantha Larson</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Scott Duffy</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Andrew Jackson</t>
+  </si>
+  <si>
+    <t>AJ</t>
+  </si>
+  <si>
+    <t>Michael Mckinney</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>19, 4, 5</t>
+  </si>
+  <si>
+    <t>Brian Wood</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Steven Martinez</t>
+  </si>
+  <si>
+    <t>SM</t>
+  </si>
+  <si>
+    <t>5, 1</t>
+  </si>
+  <si>
+    <t>Jordan Fletcher</t>
+  </si>
+  <si>
+    <t>JF</t>
+  </si>
+  <si>
+    <t>14, 15, 9</t>
+  </si>
+  <si>
+    <t>Riley Gutierrez</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>4, 8, 3</t>
+  </si>
+  <si>
+    <t>Nathan King</t>
+  </si>
+  <si>
+    <t>NK</t>
+  </si>
+  <si>
+    <t>5, 17</t>
+  </si>
+  <si>
+    <t>Jake Kelley</t>
+  </si>
+  <si>
+    <t>JK</t>
+  </si>
+  <si>
+    <t>13, 3, 17</t>
+  </si>
+  <si>
     <t>classRoomID</t>
   </si>
   <si>
+    <t>4chitm</t>
+  </si>
+  <si>
+    <t>1chitm</t>
+  </si>
+  <si>
+    <t>4ahitm</t>
+  </si>
+  <si>
+    <t>1chif</t>
+  </si>
+  <si>
+    <t>3ihf</t>
+  </si>
+  <si>
+    <t>3chitm</t>
+  </si>
+  <si>
     <t>Subject Id</t>
   </si>
   <si>
@@ -64,6 +448,48 @@
   </si>
   <si>
     <t>Is better as Double Period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
 </sst>
 </file>
@@ -108,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -123,6 +549,272 @@
       </c>
       <c r="D1" t="s" s="0">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -132,7 +824,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -140,16 +832,186 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s" s="0">
         <v>1</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>6</v>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>66.0</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>480.0</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>447.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>256.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>313.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>421.0</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>323.0</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>398.0</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>488.0</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>125.0</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -159,12 +1021,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>1</v>
@@ -173,7 +1035,287 @@
         <v>2</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>8</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -183,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -194,7 +1336,73 @@
         <v>1</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>9</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -204,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -212,22 +1420,1954 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="E1" t="s" s="0">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="F1" t="s" s="0">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="G1" t="s" s="0">
-        <v>15</v>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="B11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="B12" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B13" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B14" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="B15" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="B16" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B17" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B18" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="B19" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="B20" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="B21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n" s="0">
+        <v>21.0</v>
+      </c>
+      <c r="B22" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n" s="0">
+        <v>22.0</v>
+      </c>
+      <c r="B23" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n" s="0">
+        <v>23.0</v>
+      </c>
+      <c r="B24" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="B25" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="B26" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="B27" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n" s="0">
+        <v>27.0</v>
+      </c>
+      <c r="B28" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n" s="0">
+        <v>28.0</v>
+      </c>
+      <c r="B29" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="B30" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="B31" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="0">
+        <v>31.0</v>
+      </c>
+      <c r="B32" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n" s="0">
+        <v>32.0</v>
+      </c>
+      <c r="B33" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="B34" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n" s="0">
+        <v>34.0</v>
+      </c>
+      <c r="B35" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n" s="0">
+        <v>35.0</v>
+      </c>
+      <c r="B36" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n" s="0">
+        <v>36.0</v>
+      </c>
+      <c r="B37" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n" s="0">
+        <v>37.0</v>
+      </c>
+      <c r="B38" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n" s="0">
+        <v>38.0</v>
+      </c>
+      <c r="B39" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n" s="0">
+        <v>39.0</v>
+      </c>
+      <c r="B40" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="B41" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n" s="0">
+        <v>41.0</v>
+      </c>
+      <c r="B42" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n" s="0">
+        <v>42.0</v>
+      </c>
+      <c r="B43" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n" s="0">
+        <v>43.0</v>
+      </c>
+      <c r="B44" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n" s="0">
+        <v>44.0</v>
+      </c>
+      <c r="B45" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n" s="0">
+        <v>45.0</v>
+      </c>
+      <c r="B46" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n" s="0">
+        <v>46.0</v>
+      </c>
+      <c r="B47" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="B48" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n" s="0">
+        <v>48.0</v>
+      </c>
+      <c r="B49" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n" s="0">
+        <v>49.0</v>
+      </c>
+      <c r="B50" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n" s="0">
+        <v>50.0</v>
+      </c>
+      <c r="B51" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n" s="0">
+        <v>51.0</v>
+      </c>
+      <c r="B52" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n" s="0">
+        <v>52.0</v>
+      </c>
+      <c r="B53" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n" s="0">
+        <v>53.0</v>
+      </c>
+      <c r="B54" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n" s="0">
+        <v>54.0</v>
+      </c>
+      <c r="B55" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D55" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n" s="0">
+        <v>55.0</v>
+      </c>
+      <c r="B56" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D56" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n" s="0">
+        <v>56.0</v>
+      </c>
+      <c r="B57" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n" s="0">
+        <v>57.0</v>
+      </c>
+      <c r="B58" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n" s="0">
+        <v>58.0</v>
+      </c>
+      <c r="B59" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n" s="0">
+        <v>59.0</v>
+      </c>
+      <c r="B60" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D60" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="G60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="B61" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="D61" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n" s="0">
+        <v>61.0</v>
+      </c>
+      <c r="B62" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="D62" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n" s="0">
+        <v>62.0</v>
+      </c>
+      <c r="B63" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D63" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F63" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n" s="0">
+        <v>63.0</v>
+      </c>
+      <c r="B64" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D64" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n" s="0">
+        <v>64.0</v>
+      </c>
+      <c r="B65" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n" s="0">
+        <v>65.0</v>
+      </c>
+      <c r="B66" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="D66" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n" s="0">
+        <v>66.0</v>
+      </c>
+      <c r="B67" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n" s="0">
+        <v>67.0</v>
+      </c>
+      <c r="B68" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n" s="0">
+        <v>68.0</v>
+      </c>
+      <c r="B69" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F69" t="b">
+        <v>0</v>
+      </c>
+      <c r="G69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n" s="0">
+        <v>69.0</v>
+      </c>
+      <c r="B70" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="G70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n" s="0">
+        <v>70.0</v>
+      </c>
+      <c r="B71" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n" s="0">
+        <v>71.0</v>
+      </c>
+      <c r="B72" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n" s="0">
+        <v>72.0</v>
+      </c>
+      <c r="B73" t="n" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="B74" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F74" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n" s="0">
+        <v>74.0</v>
+      </c>
+      <c r="B75" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+      <c r="G75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n" s="0">
+        <v>75.0</v>
+      </c>
+      <c r="B76" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D76" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n" s="0">
+        <v>76.0</v>
+      </c>
+      <c r="B77" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="D77" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n" s="0">
+        <v>77.0</v>
+      </c>
+      <c r="B78" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="D78" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
+      <c r="G78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n" s="0">
+        <v>78.0</v>
+      </c>
+      <c r="B79" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n" s="0">
+        <v>79.0</v>
+      </c>
+      <c r="B80" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="B81" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="D81" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F81" t="b">
+        <v>0</v>
+      </c>
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n" s="0">
+        <v>81.0</v>
+      </c>
+      <c r="B82" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="D82" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n" s="0">
+        <v>82.0</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D83" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n" s="0">
+        <v>83.0</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="D84" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F84" t="b">
+        <v>0</v>
+      </c>
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n" s="0">
+        <v>84.0</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="D85" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
